--- a/template/2026.1.7/量化业务日报-2026-01-07.xlsx
+++ b/template/2026.1.7/量化业务日报-2026-01-07.xlsx
@@ -1971,7 +1971,7 @@
       </c>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>股票: 4 只</t>
+          <t>股票: 4 只, 开放式基金: 3 只</t>
         </is>
       </c>
     </row>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>股票: 4 只</t>
+          <t>股票: 4 只, 开放式基金: 3 只</t>
         </is>
       </c>
     </row>

--- a/template/2026.1.7/量化业务日报-2026-01-07.xlsx
+++ b/template/2026.1.7/量化业务日报-2026-01-07.xlsx
@@ -833,7 +833,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>量化二</t>
+          <t>量化测试改名</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>量化二</t>
+          <t>量化测试改名</t>
         </is>
       </c>
     </row>
